--- a/output/laminas_comunales/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>6.334091922057561</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>2.412346108075081</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>6.247226503292547</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>5.116410571690633</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>10.20322495656742</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>3.804261279149168</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>5.172330621142884</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>8.174073892942779</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>7.418455691857773</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>6.94049668337553</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>5.588565060393758</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>7.582732515556012</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>5.979531943033511</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>4.391995466305976</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>4.720839771706764</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>7.168620533696046</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>4.494828770815196</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>6.745697217297542</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>4.968049734810709</v>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>7.713562356026182</v>
       </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -844,9 +779,6 @@
       </c>
       <c r="E22">
         <v>7.642296555077577</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,380 +404,399 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B3">
-        <v>1026242.69</v>
+        <v>1031895.19</v>
       </c>
       <c r="C3">
-        <v>1002069.31</v>
+        <v>973166.1899999999</v>
       </c>
       <c r="D3">
-        <v>24173.37999999989</v>
+        <v>58729</v>
       </c>
       <c r="E3">
-        <v>2.412346108075081</v>
+        <v>6.034837687897898</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="B4">
-        <v>1021843.06</v>
+        <v>1026242.69</v>
       </c>
       <c r="C4">
-        <v>961759.75</v>
+        <v>1002069.31</v>
       </c>
       <c r="D4">
-        <v>60083.31000000006</v>
+        <v>24173.37999999989</v>
       </c>
       <c r="E4">
-        <v>6.247226503292547</v>
+        <v>2.412346108075081</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="B5">
-        <v>1016256.06</v>
+        <v>1021843.06</v>
       </c>
       <c r="C5">
-        <v>966791.0600000001</v>
+        <v>961759.75</v>
       </c>
       <c r="D5">
-        <v>49465</v>
+        <v>60083.31000000006</v>
       </c>
       <c r="E5">
-        <v>5.116410571690633</v>
+        <v>6.247226503292547</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B6">
-        <v>989245.3100000001</v>
+        <v>1016256.06</v>
       </c>
       <c r="C6">
-        <v>897655.5</v>
+        <v>966791.0600000001</v>
       </c>
       <c r="D6">
-        <v>91589.81000000006</v>
+        <v>49465</v>
       </c>
       <c r="E6">
-        <v>10.20322495656742</v>
+        <v>5.116410571690633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="B7">
-        <v>984028.1899999999</v>
+        <v>989245.3100000001</v>
       </c>
       <c r="C7">
-        <v>947965.12</v>
+        <v>897655.5</v>
       </c>
       <c r="D7">
-        <v>36063.06999999995</v>
+        <v>91589.81000000006</v>
       </c>
       <c r="E7">
-        <v>3.804261279149168</v>
+        <v>10.20322495656742</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="B8">
-        <v>981526.5600000001</v>
+        <v>984028.1899999999</v>
       </c>
       <c r="C8">
-        <v>933255.5</v>
+        <v>947965.12</v>
       </c>
       <c r="D8">
-        <v>48271.06000000006</v>
+        <v>36063.06999999995</v>
       </c>
       <c r="E8">
-        <v>5.172330621142884</v>
+        <v>3.804261279149168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="B9">
-        <v>976776.0600000001</v>
+        <v>981526.5600000001</v>
       </c>
       <c r="C9">
-        <v>902966.88</v>
+        <v>933255.5</v>
       </c>
       <c r="D9">
-        <v>73809.18000000005</v>
+        <v>48271.06000000006</v>
       </c>
       <c r="E9">
-        <v>8.174073892942779</v>
+        <v>5.172330621142884</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="B10">
-        <v>960654.12</v>
+        <v>976776.0600000001</v>
       </c>
       <c r="C10">
-        <v>894310.12</v>
+        <v>902966.88</v>
       </c>
       <c r="D10">
-        <v>66344</v>
+        <v>73809.18000000005</v>
       </c>
       <c r="E10">
-        <v>7.418455691857773</v>
+        <v>8.174073892942779</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="B11">
-        <v>959673.12</v>
+        <v>960654.12</v>
       </c>
       <c r="C11">
-        <v>897389.8100000001</v>
+        <v>894310.12</v>
       </c>
       <c r="D11">
-        <v>62283.30999999994</v>
+        <v>66344</v>
       </c>
       <c r="E11">
-        <v>6.94049668337553</v>
+        <v>7.418455691857773</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="B12">
-        <v>941440.1899999999</v>
+        <v>959673.12</v>
       </c>
       <c r="C12">
-        <v>891611.88</v>
+        <v>897389.8100000001</v>
       </c>
       <c r="D12">
-        <v>49828.30999999994</v>
+        <v>62283.30999999994</v>
       </c>
       <c r="E12">
-        <v>5.588565060393758</v>
+        <v>6.94049668337553</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="B13">
-        <v>914172.5</v>
+        <v>941440.1899999999</v>
       </c>
       <c r="C13">
-        <v>849739.0600000001</v>
+        <v>891611.88</v>
       </c>
       <c r="D13">
-        <v>64433.43999999994</v>
+        <v>49828.30999999994</v>
       </c>
       <c r="E13">
-        <v>7.582732515556012</v>
+        <v>5.588565060393758</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="B14">
-        <v>913319.62</v>
+        <v>914172.5</v>
       </c>
       <c r="C14">
-        <v>861788.6899999999</v>
+        <v>849739.0600000001</v>
       </c>
       <c r="D14">
-        <v>51530.93000000005</v>
+        <v>64433.43999999994</v>
       </c>
       <c r="E14">
-        <v>5.979531943033511</v>
+        <v>7.582732515556012</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="B15">
-        <v>911122.25</v>
+        <v>913319.62</v>
       </c>
       <c r="C15">
-        <v>872789.38</v>
+        <v>861788.6899999999</v>
       </c>
       <c r="D15">
-        <v>38332.87</v>
+        <v>51530.93000000005</v>
       </c>
       <c r="E15">
-        <v>4.391995466305976</v>
+        <v>5.979531943033511</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="B16">
-        <v>899169.0600000001</v>
+        <v>911122.25</v>
       </c>
       <c r="C16">
-        <v>858634.3100000001</v>
+        <v>872789.38</v>
       </c>
       <c r="D16">
-        <v>40534.75</v>
+        <v>38332.87</v>
       </c>
       <c r="E16">
-        <v>4.720839771706764</v>
+        <v>4.391995466305976</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="B17">
-        <v>885439.0600000001</v>
+        <v>899169.0600000001</v>
       </c>
       <c r="C17">
-        <v>826211.12</v>
+        <v>858634.3100000001</v>
       </c>
       <c r="D17">
-        <v>59227.94000000006</v>
+        <v>40534.75</v>
       </c>
       <c r="E17">
-        <v>7.168620533696046</v>
+        <v>4.720839771706764</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="B18">
-        <v>871215.0600000001</v>
+        <v>885439.0600000001</v>
       </c>
       <c r="C18">
-        <v>833739.88</v>
+        <v>826211.12</v>
       </c>
       <c r="D18">
-        <v>37475.18000000005</v>
+        <v>59227.94000000006</v>
       </c>
       <c r="E18">
-        <v>4.494828770815196</v>
+        <v>7.168620533696046</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="B19">
-        <v>869097.25</v>
+        <v>871215.0600000001</v>
       </c>
       <c r="C19">
-        <v>814175.4399999999</v>
+        <v>833739.88</v>
       </c>
       <c r="D19">
-        <v>54921.81000000006</v>
+        <v>37475.18000000005</v>
       </c>
       <c r="E19">
-        <v>6.745697217297542</v>
+        <v>4.494828770815196</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="B20">
-        <v>859250.8100000001</v>
+        <v>869097.25</v>
       </c>
       <c r="C20">
-        <v>818583.1899999999</v>
+        <v>814175.4399999999</v>
       </c>
       <c r="D20">
-        <v>40667.62000000011</v>
+        <v>54921.81000000006</v>
       </c>
       <c r="E20">
-        <v>4.968049734810709</v>
+        <v>6.745697217297542</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="B21">
-        <v>826594.75</v>
+        <v>859250.8100000001</v>
       </c>
       <c r="C21">
-        <v>767400.8100000001</v>
+        <v>818583.1899999999</v>
       </c>
       <c r="D21">
-        <v>59193.93999999994</v>
+        <v>40667.62000000011</v>
       </c>
       <c r="E21">
-        <v>7.713562356026182</v>
+        <v>4.968049734810709</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>826594.75</v>
+      </c>
+      <c r="C22">
+        <v>767400.8100000001</v>
+      </c>
+      <c r="D22">
+        <v>59193.93999999994</v>
+      </c>
+      <c r="E22">
+        <v>7.713562356026182</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Ninhue</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>824528.5600000001</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>765989.38</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>58539.18000000005</v>
       </c>
-      <c r="E22">
+      <c r="E23">
         <v>7.642296555077577</v>
       </c>
     </row>
@@ -946,7 +965,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B16">

--- a/output/laminas_comunales/comunal_i_ingr_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_nuble.xlsx
@@ -807,7 +807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -816,11 +816,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -828,9 +823,6 @@
           <t>Bulnes</t>
         </is>
       </c>
-      <c r="B2">
-        <v>941440.1899999999</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -838,9 +830,6 @@
           <t>Chillán Viejo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>1021843.06</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,188 +837,131 @@
           <t>Chillán</t>
         </is>
       </c>
-      <c r="B4">
-        <v>1149787.75</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>911122.25</v>
+          <t>Yungay</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coelemu</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>981526.5600000001</v>
+          <t>Quillón</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coihueco</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>885439.0600000001</v>
+          <t>San Carlos</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El Carmen</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>869097.25</v>
+          <t>Treguaco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ninhue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>824528.5600000001</v>
+          <t>Ranquil</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>989245.3100000001</v>
+          <t>Portezuelo</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pemuco</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>871215.0600000001</v>
+          <t>Cobquecura</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pinto</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>960654.12</v>
+          <t>Quirihue</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>859250.8100000001</v>
+          <t>Coelemu</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quillón</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>984028.1899999999</v>
+          <t>Ninhue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quirihue</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>899169.0600000001</v>
+          <t>Pinto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ranquil</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>1016256.06</v>
+          <t>San Ignacio</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>976776.0600000001</v>
+          <t>Pemuco</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Fabián</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>959673.12</v>
+          <t>San Nicolás</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>826594.75</v>
+          <t>San Fabián</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>913319.62</v>
+          <t>Ñiquén</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Treguaco</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>914172.5</v>
+          <t>El Carmen</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yungay</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>1026242.69</v>
+          <t>Coihueco</t>
+        </is>
       </c>
     </row>
   </sheetData>
